--- a/AZ Phase 3 Virus Inactivation and filtration/AZ Phase 3 VI + CDF - Traceability Matrix (RTM).xlsx
+++ b/AZ Phase 3 Virus Inactivation and filtration/AZ Phase 3 VI + CDF - Traceability Matrix (RTM).xlsx
@@ -4174,7 +4174,7 @@
       <c r="G70" s="12" t="inlineStr"/>
       <c r="H70" s="12" t="inlineStr">
         <is>
-          <t>SMPL: VI Treatment Vessel Setup (Comprehensive)</t>
+          <t>SMPL: VI Treatment Vessel Setup</t>
         </is>
       </c>
       <c r="I70" s="12" t="inlineStr">
@@ -4222,7 +4222,7 @@
       <c r="G71" s="12" t="inlineStr"/>
       <c r="H71" s="12" t="inlineStr">
         <is>
-          <t>SMPL: VI Treatment Vessel Setup (Comprehensive)</t>
+          <t>SMPL: VI Treatment Vessel Setup</t>
         </is>
       </c>
       <c r="I71" s="12" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="H72" s="12" t="inlineStr">
         <is>
-          <t>SMPL: VI Treatment Vessel Setup (Comprehensive)</t>
+          <t>SMPL: VI Treatment Vessel Setup</t>
         </is>
       </c>
       <c r="I72" s="12" t="inlineStr">
@@ -4322,7 +4322,7 @@
       <c r="G73" s="12" t="inlineStr"/>
       <c r="H73" s="12" t="inlineStr">
         <is>
-          <t>SMPL: VI Treatment Vessel Setup (Comprehensive)</t>
+          <t>SMPL: VI Treatment Vessel Setup</t>
         </is>
       </c>
       <c r="I73" s="12" t="inlineStr">
@@ -4370,7 +4370,7 @@
       <c r="G74" s="12" t="inlineStr"/>
       <c r="H74" s="12" t="inlineStr">
         <is>
-          <t>SMPL: VI Treatment Vessel Setup (Comprehensive)</t>
+          <t>SMPL: VI Treatment Vessel Setup</t>
         </is>
       </c>
       <c r="I74" s="12" t="inlineStr">
@@ -4418,7 +4418,7 @@
       <c r="G75" s="12" t="inlineStr"/>
       <c r="H75" s="12" t="inlineStr">
         <is>
-          <t>SMPL: VI Treatment Vessel Setup (Comprehensive)</t>
+          <t>SMPL: VI Treatment Vessel Setup</t>
         </is>
       </c>
       <c r="I75" s="12" t="inlineStr">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="H76" s="12" t="inlineStr">
         <is>
-          <t>SMPL: VI Treatment Vessel Setup (Comprehensive)</t>
+          <t>SMPL: VI Treatment Vessel Setup</t>
         </is>
       </c>
       <c r="I76" s="12" t="inlineStr">
@@ -4522,7 +4522,7 @@
       </c>
       <c r="H77" s="12" t="inlineStr">
         <is>
-          <t>SMPL: VI Treatment Vessel Setup (Comprehensive)</t>
+          <t>SMPL: VI Treatment Vessel Setup</t>
         </is>
       </c>
       <c r="I77" s="12" t="inlineStr">
@@ -4574,7 +4574,7 @@
       </c>
       <c r="H78" s="12" t="inlineStr">
         <is>
-          <t>SMPL: VI Treatment Vessel Setup (Comprehensive)</t>
+          <t>SMPL: VI Treatment Vessel Setup</t>
         </is>
       </c>
       <c r="I78" s="12" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="H79" s="12" t="inlineStr">
         <is>
-          <t>SMPL: VI Treatment Vessel Setup (Comprehensive)</t>
+          <t>SMPL: VI Treatment Vessel Setup</t>
         </is>
       </c>
       <c r="I79" s="12" t="inlineStr">
@@ -4678,7 +4678,7 @@
       </c>
       <c r="H80" s="12" t="inlineStr">
         <is>
-          <t>SMPL: VI Treatment Vessel Setup (Comprehensive)</t>
+          <t>SMPL: VI Treatment Vessel Setup</t>
         </is>
       </c>
       <c r="I80" s="12" t="inlineStr">
@@ -4726,7 +4726,7 @@
       <c r="G81" s="12" t="inlineStr"/>
       <c r="H81" s="12" t="inlineStr">
         <is>
-          <t>SMPL: VI Treatment Vessel Setup (Comprehensive)</t>
+          <t>SMPL: VI Treatment Vessel Setup</t>
         </is>
       </c>
       <c r="I81" s="12" t="inlineStr">
@@ -4774,7 +4774,7 @@
       <c r="G82" s="12" t="inlineStr"/>
       <c r="H82" s="12" t="inlineStr">
         <is>
-          <t>SMPL: VI Treatment Vessel Setup (Comprehensive)</t>
+          <t>SMPL: VI Treatment Vessel Setup</t>
         </is>
       </c>
       <c r="I82" s="12" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="H83" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Starting / Transfer Temperature Decision</t>
+          <t>SMPL: Starting / Transfer Temperature Decision (block stack)</t>
         </is>
       </c>
       <c r="I83" s="12" t="inlineStr">
@@ -4878,7 +4878,7 @@
       </c>
       <c r="H84" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Starting / Transfer Temperature Decision</t>
+          <t>SMPL: Starting / Transfer Temperature Decision (block stack)</t>
         </is>
       </c>
       <c r="I84" s="12" t="inlineStr">
@@ -4930,7 +4930,7 @@
       </c>
       <c r="H85" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Starting / Transfer Temperature Decision</t>
+          <t>SMPL: Starting / Transfer Temperature Decision (block stack)</t>
         </is>
       </c>
       <c r="I85" s="12" t="inlineStr">
@@ -4982,7 +4982,7 @@
       </c>
       <c r="H86" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Starting / Transfer Temperature Decision</t>
+          <t>SMPL: Starting / Transfer Temperature Decision (block stack)</t>
         </is>
       </c>
       <c r="I86" s="12" t="inlineStr">
@@ -5030,7 +5030,7 @@
       <c r="G87" s="12" t="inlineStr"/>
       <c r="H87" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Starting / Transfer Temperature Decision</t>
+          <t>SMPL: Starting / Transfer Temperature Decision (block stack)</t>
         </is>
       </c>
       <c r="I87" s="12" t="inlineStr">
@@ -5078,7 +5078,7 @@
       <c r="G88" s="12" t="inlineStr"/>
       <c r="H88" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Starting / Transfer Temperature Decision</t>
+          <t>SMPL: Starting / Transfer Temperature Decision (block stack)</t>
         </is>
       </c>
       <c r="I88" s="12" t="inlineStr">
@@ -5130,7 +5130,7 @@
       </c>
       <c r="H89" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Starting / Transfer Temperature Decision</t>
+          <t>SMPL: Starting / Transfer Temperature Decision (block stack)</t>
         </is>
       </c>
       <c r="I89" s="12" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="H105" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Incubation Timing &amp; Incubated Sample</t>
+          <t>SMPL: Incubation Timing &amp; Incubated Sample (block stack)</t>
         </is>
       </c>
       <c r="I105" s="12" t="inlineStr">
@@ -5970,7 +5970,7 @@
       </c>
       <c r="H106" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Incubation Timing &amp; Incubated Sample</t>
+          <t>SMPL: Incubation Timing &amp; Incubated Sample (block stack)</t>
         </is>
       </c>
       <c r="I106" s="12" t="inlineStr">
@@ -6022,7 +6022,7 @@
       </c>
       <c r="H107" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Incubation Timing &amp; Incubated Sample</t>
+          <t>SMPL: Incubation Timing &amp; Incubated Sample (block stack)</t>
         </is>
       </c>
       <c r="I107" s="12" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="H118" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Incubation Timing &amp; Incubated Sample</t>
+          <t>SMPL: Incubation Timing &amp; Incubated Sample (block stack)</t>
         </is>
       </c>
       <c r="I118" s="12" t="inlineStr">
@@ -6618,7 +6618,7 @@
       </c>
       <c r="H119" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Incubation Timing &amp; Incubated Sample</t>
+          <t>SMPL: Incubation Timing &amp; Incubated Sample (block stack)</t>
         </is>
       </c>
       <c r="I119" s="12" t="inlineStr">
@@ -6670,7 +6670,7 @@
       </c>
       <c r="H120" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Incubation Timing &amp; Incubated Sample</t>
+          <t>SMPL: Incubation Timing &amp; Incubated Sample (block stack)</t>
         </is>
       </c>
       <c r="I120" s="12" t="inlineStr">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="H121" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Incubation Timing &amp; Incubated Sample</t>
+          <t>SMPL: Incubation Timing &amp; Incubated Sample (block stack)</t>
         </is>
       </c>
       <c r="I121" s="12" t="inlineStr">
@@ -6770,7 +6770,7 @@
       <c r="G122" s="12" t="inlineStr"/>
       <c r="H122" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Incubation Timing &amp; Incubated Sample</t>
+          <t>SMPL: Incubation Timing &amp; Incubated Sample (block stack)</t>
         </is>
       </c>
       <c r="I122" s="12" t="inlineStr">
@@ -6822,7 +6822,7 @@
       </c>
       <c r="H123" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Incubation Timing &amp; Incubated Sample</t>
+          <t>SMPL: Incubation Timing &amp; Incubated Sample (block stack)</t>
         </is>
       </c>
       <c r="I123" s="12" t="inlineStr">
@@ -12010,7 +12010,7 @@
       </c>
       <c r="H229" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Calculate Minimum Membrane Surface Area</t>
+          <t>SMPL: Minimum Membrane Surface Area (block stack)</t>
         </is>
       </c>
       <c r="I229" s="12" t="inlineStr">
@@ -12062,7 +12062,7 @@
       </c>
       <c r="H230" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Calculate Minimum Membrane Surface Area</t>
+          <t>SMPL: Minimum Membrane Surface Area (block stack)</t>
         </is>
       </c>
       <c r="I230" s="12" t="inlineStr">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="H231" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Calculate Minimum Membrane Surface Area</t>
+          <t>SMPL: Minimum Membrane Surface Area (block stack)</t>
         </is>
       </c>
       <c r="I231" s="12" t="inlineStr">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="H232" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Calculate Minimum Membrane Surface Area</t>
+          <t>SMPL: Minimum Membrane Surface Area (block stack)</t>
         </is>
       </c>
       <c r="I232" s="12" t="inlineStr">
@@ -12218,7 +12218,7 @@
       </c>
       <c r="H233" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Calculate Minimum Membrane Surface Area</t>
+          <t>SMPL: Minimum Membrane Surface Area (block stack)</t>
         </is>
       </c>
       <c r="I233" s="12" t="inlineStr">
@@ -12270,7 +12270,7 @@
       </c>
       <c r="H234" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Calculate Minimum Membrane Surface Area</t>
+          <t>SMPL: Minimum Membrane Surface Area (block stack)</t>
         </is>
       </c>
       <c r="I234" s="12" t="inlineStr">
@@ -12322,7 +12322,7 @@
       </c>
       <c r="H235" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Calculate Minimum Membrane Surface Area</t>
+          <t>SMPL: Minimum Membrane Surface Area (block stack)</t>
         </is>
       </c>
       <c r="I235" s="12" t="inlineStr">
@@ -12370,7 +12370,7 @@
       <c r="G236" s="12" t="inlineStr"/>
       <c r="H236" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Calculate Minimum Membrane Surface Area</t>
+          <t>SMPL: Minimum Membrane Surface Area (block stack)</t>
         </is>
       </c>
       <c r="I236" s="12" t="inlineStr">
@@ -12422,7 +12422,7 @@
       </c>
       <c r="H237" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I237" s="12" t="inlineStr">
@@ -12470,7 +12470,7 @@
       <c r="G238" s="12" t="inlineStr"/>
       <c r="H238" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I238" s="12" t="inlineStr">
@@ -12522,7 +12522,7 @@
       </c>
       <c r="H239" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I239" s="12" t="inlineStr">
@@ -12574,7 +12574,7 @@
       </c>
       <c r="H240" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I240" s="12" t="inlineStr">
@@ -12622,7 +12622,7 @@
       <c r="G241" s="12" t="inlineStr"/>
       <c r="H241" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I241" s="12" t="inlineStr">
@@ -12670,7 +12670,7 @@
       <c r="G242" s="12" t="inlineStr"/>
       <c r="H242" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I242" s="12" t="inlineStr">
@@ -12718,7 +12718,7 @@
       <c r="G243" s="12" t="inlineStr"/>
       <c r="H243" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I243" s="12" t="inlineStr">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="H244" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I244" s="12" t="inlineStr">
@@ -12822,7 +12822,7 @@
       </c>
       <c r="H245" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I245" s="12" t="inlineStr">
@@ -12874,7 +12874,7 @@
       </c>
       <c r="H246" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I246" s="12" t="inlineStr">
@@ -12926,7 +12926,7 @@
       </c>
       <c r="H247" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I247" s="12" t="inlineStr">
@@ -12974,7 +12974,7 @@
       <c r="G248" s="12" t="inlineStr"/>
       <c r="H248" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I248" s="12" t="inlineStr">
@@ -13022,7 +13022,7 @@
       <c r="G249" s="12" t="inlineStr"/>
       <c r="H249" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I249" s="12" t="inlineStr">
@@ -13074,7 +13074,7 @@
       </c>
       <c r="H250" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I250" s="12" t="inlineStr">
@@ -13122,7 +13122,7 @@
       <c r="G251" s="12" t="inlineStr"/>
       <c r="H251" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I251" s="12" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="H252" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I252" s="12" t="inlineStr">
@@ -13226,7 +13226,7 @@
       </c>
       <c r="H253" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I253" s="12" t="inlineStr">
@@ -13274,7 +13274,7 @@
       <c r="G254" s="12" t="inlineStr"/>
       <c r="H254" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I254" s="12" t="inlineStr">
@@ -13322,7 +13322,7 @@
       <c r="G255" s="12" t="inlineStr"/>
       <c r="H255" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I255" s="12" t="inlineStr">
@@ -13374,7 +13374,7 @@
       </c>
       <c r="H256" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I256" s="12" t="inlineStr">
@@ -13422,7 +13422,7 @@
       <c r="G257" s="12" t="inlineStr"/>
       <c r="H257" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Hold Time Table</t>
+          <t>SMPL: Product Mixing</t>
         </is>
       </c>
       <c r="I257" s="12" t="inlineStr">
@@ -13474,7 +13474,7 @@
       </c>
       <c r="H258" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Hold Time Table</t>
+          <t>SMPL: Product Mixing</t>
         </is>
       </c>
       <c r="I258" s="12" t="inlineStr">
@@ -13526,7 +13526,7 @@
       </c>
       <c r="H259" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Hold Time Table</t>
+          <t>SMPL: Product Mixing</t>
         </is>
       </c>
       <c r="I259" s="12" t="inlineStr">
@@ -13574,7 +13574,7 @@
       <c r="G260" s="12" t="inlineStr"/>
       <c r="H260" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Hold Time Table</t>
+          <t>SMPL: Product Mixing</t>
         </is>
       </c>
       <c r="I260" s="12" t="inlineStr">
@@ -13622,7 +13622,7 @@
       <c r="G261" s="12" t="inlineStr"/>
       <c r="H261" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Hold Time Table</t>
+          <t>SMPL: Product Mixing</t>
         </is>
       </c>
       <c r="I261" s="12" t="inlineStr">
@@ -13674,7 +13674,7 @@
       </c>
       <c r="H262" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Hold Time Table</t>
+          <t>SMPL: Product Mixing</t>
         </is>
       </c>
       <c r="I262" s="12" t="inlineStr">
@@ -13722,7 +13722,7 @@
       <c r="G263" s="12" t="inlineStr"/>
       <c r="H263" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Hold Time Table</t>
+          <t>SMPL: Product Mixing</t>
         </is>
       </c>
       <c r="I263" s="12" t="inlineStr">
@@ -13774,7 +13774,7 @@
       </c>
       <c r="H264" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Hold Time Table</t>
+          <t>SMPL: Product Mixing</t>
         </is>
       </c>
       <c r="I264" s="12" t="inlineStr">
@@ -13826,7 +13826,7 @@
       </c>
       <c r="H265" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Hold Time Table</t>
+          <t>SMPL: Product Mixing</t>
         </is>
       </c>
       <c r="I265" s="12" t="inlineStr">
@@ -13878,7 +13878,7 @@
       </c>
       <c r="H266" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Hold Time Table</t>
+          <t>SMPL: Product Mixing</t>
         </is>
       </c>
       <c r="I266" s="12" t="inlineStr">
@@ -13926,7 +13926,7 @@
       <c r="G267" s="12" t="inlineStr"/>
       <c r="H267" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I267" s="12" t="inlineStr">
@@ -13974,7 +13974,7 @@
       <c r="G268" s="12" t="inlineStr"/>
       <c r="H268" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I268" s="12" t="inlineStr">
@@ -14026,7 +14026,7 @@
       </c>
       <c r="H269" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I269" s="12" t="inlineStr">
@@ -14078,7 +14078,7 @@
       </c>
       <c r="H270" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I270" s="12" t="inlineStr">
@@ -14130,7 +14130,7 @@
       </c>
       <c r="H271" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I271" s="12" t="inlineStr">
@@ -14178,7 +14178,7 @@
       <c r="G272" s="12" t="inlineStr"/>
       <c r="H272" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I272" s="12" t="inlineStr">
@@ -14230,7 +14230,7 @@
       </c>
       <c r="H273" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I273" s="12" t="inlineStr">
@@ -14282,7 +14282,7 @@
       </c>
       <c r="H274" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I274" s="12" t="inlineStr">
@@ -14330,7 +14330,7 @@
       <c r="G275" s="12" t="inlineStr"/>
       <c r="H275" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I275" s="12" t="inlineStr">
@@ -14382,7 +14382,7 @@
       </c>
       <c r="H276" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I276" s="12" t="inlineStr">
@@ -14434,7 +14434,7 @@
       </c>
       <c r="H277" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I277" s="12" t="inlineStr">
@@ -14482,7 +14482,7 @@
       <c r="G278" s="12" t="inlineStr"/>
       <c r="H278" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I278" s="12" t="inlineStr">
@@ -14534,7 +14534,7 @@
       </c>
       <c r="H279" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I279" s="12" t="inlineStr">
@@ -14586,7 +14586,7 @@
       </c>
       <c r="H280" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I280" s="12" t="inlineStr">
@@ -14638,7 +14638,7 @@
       </c>
       <c r="H281" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I281" s="12" t="inlineStr">
@@ -14690,7 +14690,7 @@
       </c>
       <c r="H282" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Record CIPDS / Skid / Cassette Information</t>
+          <t>SMPL: Record CIPDS / Skid / Cassette Information (block stack)</t>
         </is>
       </c>
       <c r="I282" s="12" t="inlineStr">
@@ -14738,7 +14738,7 @@
       <c r="G283" s="12" t="inlineStr"/>
       <c r="H283" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Record CIPDS / Skid / Cassette Information</t>
+          <t>SMPL: Record CIPDS / Skid / Cassette Information (block stack)</t>
         </is>
       </c>
       <c r="I283" s="12" t="inlineStr">
@@ -14786,7 +14786,7 @@
       <c r="G284" s="12" t="inlineStr"/>
       <c r="H284" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Record CIPDS / Skid / Cassette Information</t>
+          <t>SMPL: Record CIPDS / Skid / Cassette Information (block stack)</t>
         </is>
       </c>
       <c r="I284" s="12" t="inlineStr">
@@ -14834,7 +14834,7 @@
       <c r="G285" s="12" t="inlineStr"/>
       <c r="H285" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Record CIPDS / Skid / Cassette Information</t>
+          <t>SMPL: Record CIPDS / Skid / Cassette Information (block stack)</t>
         </is>
       </c>
       <c r="I285" s="12" t="inlineStr">
@@ -14886,7 +14886,7 @@
       </c>
       <c r="H286" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Record CIPDS / Skid / Cassette Information</t>
+          <t>SMPL: Record CIPDS / Skid / Cassette Information (block stack)</t>
         </is>
       </c>
       <c r="I286" s="12" t="inlineStr">
@@ -14938,7 +14938,7 @@
       </c>
       <c r="H287" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Record CIPDS / Skid / Cassette Information</t>
+          <t>SMPL: Record CIPDS / Skid / Cassette Information (block stack)</t>
         </is>
       </c>
       <c r="I287" s="12" t="inlineStr">
@@ -14990,7 +14990,7 @@
       </c>
       <c r="H288" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Record CIPDS / Skid / Cassette Information</t>
+          <t>SMPL: Record CIPDS / Skid / Cassette Information (block stack)</t>
         </is>
       </c>
       <c r="I288" s="12" t="inlineStr">
@@ -15038,7 +15038,7 @@
       <c r="G289" s="12" t="inlineStr"/>
       <c r="H289" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Record CIPDS / Skid / Cassette Information</t>
+          <t>SMPL: Record CIPDS / Skid / Cassette Information (block stack)</t>
         </is>
       </c>
       <c r="I289" s="12" t="inlineStr">
@@ -15090,7 +15090,7 @@
       </c>
       <c r="H290" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Record CIPDS / Skid / Cassette Information</t>
+          <t>SMPL: Record CIPDS / Skid / Cassette Information (block stack)</t>
         </is>
       </c>
       <c r="I290" s="12" t="inlineStr">
@@ -15142,7 +15142,7 @@
       </c>
       <c r="H291" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Record CIPDS / Skid / Cassette Information</t>
+          <t>SMPL: Record CIPDS / Skid / Cassette Information (block stack)</t>
         </is>
       </c>
       <c r="I291" s="12" t="inlineStr">
@@ -15194,7 +15194,7 @@
       </c>
       <c r="H292" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Record CIPDS / Skid / Cassette Information</t>
+          <t>SMPL: Record CIPDS / Skid / Cassette Information (block stack)</t>
         </is>
       </c>
       <c r="I292" s="12" t="inlineStr">
@@ -15246,7 +15246,7 @@
       </c>
       <c r="H293" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Process Input Calculations</t>
+          <t>SMPL: Process Input Calculations (calc-block stack)</t>
         </is>
       </c>
       <c r="I293" s="12" t="inlineStr">
@@ -15298,7 +15298,7 @@
       </c>
       <c r="H294" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Process Input Calculations</t>
+          <t>SMPL: Process Input Calculations (calc-block stack)</t>
         </is>
       </c>
       <c r="I294" s="12" t="inlineStr">
@@ -15350,7 +15350,7 @@
       </c>
       <c r="H295" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Process Input Calculations</t>
+          <t>SMPL: Process Input Calculations (calc-block stack)</t>
         </is>
       </c>
       <c r="I295" s="12" t="inlineStr">
@@ -15402,7 +15402,7 @@
       </c>
       <c r="H296" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Process Input Calculations</t>
+          <t>SMPL: Process Input Calculations (calc-block stack)</t>
         </is>
       </c>
       <c r="I296" s="12" t="inlineStr">
@@ -15454,7 +15454,7 @@
       </c>
       <c r="H297" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Process Input Calculations</t>
+          <t>SMPL: Process Input Calculations (calc-block stack)</t>
         </is>
       </c>
       <c r="I297" s="12" t="inlineStr">
@@ -15506,7 +15506,7 @@
       </c>
       <c r="H298" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Process Input Calculations</t>
+          <t>SMPL: Process Input Calculations (calc-block stack)</t>
         </is>
       </c>
       <c r="I298" s="12" t="inlineStr">
@@ -15558,7 +15558,7 @@
       </c>
       <c r="H299" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Process Input Calculations</t>
+          <t>SMPL: Process Input Calculations (calc-block stack)</t>
         </is>
       </c>
       <c r="I299" s="12" t="inlineStr">
@@ -15610,7 +15610,7 @@
       </c>
       <c r="H300" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Process Input Calculations</t>
+          <t>SMPL: Process Input Calculations (calc-block stack)</t>
         </is>
       </c>
       <c r="I300" s="12" t="inlineStr">
@@ -15662,7 +15662,7 @@
       </c>
       <c r="H301" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Process Input Calculations</t>
+          <t>SMPL: Process Input Calculations (calc-block stack)</t>
         </is>
       </c>
       <c r="I301" s="12" t="inlineStr">
@@ -15710,7 +15710,7 @@
       <c r="G302" s="12" t="inlineStr"/>
       <c r="H302" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I302" s="12" t="inlineStr">
@@ -15762,7 +15762,7 @@
       </c>
       <c r="H303" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I303" s="12" t="inlineStr">
@@ -15810,7 +15810,7 @@
       <c r="G304" s="12" t="inlineStr"/>
       <c r="H304" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I304" s="12" t="inlineStr">
@@ -15862,7 +15862,7 @@
       </c>
       <c r="H305" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I305" s="12" t="inlineStr">
@@ -15914,7 +15914,7 @@
       </c>
       <c r="H306" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I306" s="12" t="inlineStr">
@@ -15962,7 +15962,7 @@
       <c r="G307" s="12" t="inlineStr"/>
       <c r="H307" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I307" s="12" t="inlineStr">
@@ -16014,7 +16014,7 @@
       </c>
       <c r="H308" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I308" s="12" t="inlineStr">
@@ -16066,7 +16066,7 @@
       </c>
       <c r="H309" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I309" s="12" t="inlineStr">
@@ -16118,7 +16118,7 @@
       </c>
       <c r="H310" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I310" s="12" t="inlineStr">
@@ -16170,7 +16170,7 @@
       </c>
       <c r="H311" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I311" s="12" t="inlineStr">
@@ -16218,7 +16218,7 @@
       <c r="G312" s="12" t="inlineStr"/>
       <c r="H312" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I312" s="12" t="inlineStr">
@@ -16266,7 +16266,7 @@
       <c r="G313" s="12" t="inlineStr"/>
       <c r="H313" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I313" s="12" t="inlineStr">
@@ -16314,7 +16314,7 @@
       <c r="G314" s="12" t="inlineStr"/>
       <c r="H314" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I314" s="12" t="inlineStr">
@@ -16362,7 +16362,7 @@
       <c r="G315" s="12" t="inlineStr"/>
       <c r="H315" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I315" s="12" t="inlineStr">
@@ -16414,7 +16414,7 @@
       </c>
       <c r="H316" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I316" s="12" t="inlineStr">
@@ -16466,7 +16466,7 @@
       </c>
       <c r="H317" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I317" s="12" t="inlineStr">
@@ -16514,7 +16514,7 @@
       <c r="G318" s="12" t="inlineStr"/>
       <c r="H318" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I318" s="12" t="inlineStr">
@@ -16566,7 +16566,7 @@
       </c>
       <c r="H319" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I319" s="12" t="inlineStr">
@@ -16614,7 +16614,7 @@
       <c r="G320" s="12" t="inlineStr"/>
       <c r="H320" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I320" s="12" t="inlineStr">
@@ -16666,7 +16666,7 @@
       </c>
       <c r="H321" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I321" s="12" t="inlineStr">
@@ -16718,7 +16718,7 @@
       </c>
       <c r="H322" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I322" s="12" t="inlineStr">
@@ -16766,7 +16766,7 @@
       <c r="G323" s="12" t="inlineStr"/>
       <c r="H323" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I323" s="12" t="inlineStr">
@@ -16818,7 +16818,7 @@
       </c>
       <c r="H324" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I324" s="12" t="inlineStr">
@@ -16866,7 +16866,7 @@
       <c r="G325" s="12" t="inlineStr"/>
       <c r="H325" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I325" s="12" t="inlineStr">
@@ -16918,7 +16918,7 @@
       </c>
       <c r="H326" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I326" s="12" t="inlineStr">
@@ -16970,7 +16970,7 @@
       </c>
       <c r="H327" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I327" s="12" t="inlineStr">
@@ -17022,7 +17022,7 @@
       </c>
       <c r="H328" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I328" s="12" t="inlineStr">
@@ -17070,7 +17070,7 @@
       <c r="G329" s="12" t="inlineStr"/>
       <c r="H329" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I329" s="12" t="inlineStr">
@@ -17122,7 +17122,7 @@
       </c>
       <c r="H330" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I330" s="12" t="inlineStr">
@@ -17174,7 +17174,7 @@
       </c>
       <c r="H331" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I331" s="12" t="inlineStr">
@@ -17222,7 +17222,7 @@
       <c r="G332" s="12" t="inlineStr"/>
       <c r="H332" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I332" s="12" t="inlineStr">
@@ -17274,7 +17274,7 @@
       </c>
       <c r="H333" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I333" s="12" t="inlineStr">
@@ -17326,7 +17326,7 @@
       </c>
       <c r="H334" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I334" s="12" t="inlineStr">
@@ -17378,7 +17378,7 @@
       </c>
       <c r="H335" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I335" s="12" t="inlineStr">
@@ -17426,7 +17426,7 @@
       <c r="G336" s="12" t="inlineStr"/>
       <c r="H336" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I336" s="12" t="inlineStr">
@@ -17478,7 +17478,7 @@
       </c>
       <c r="H337" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I337" s="12" t="inlineStr">
@@ -17530,7 +17530,7 @@
       </c>
       <c r="H338" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I338" s="12" t="inlineStr">
@@ -17582,7 +17582,7 @@
       </c>
       <c r="H339" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I339" s="12" t="inlineStr">
@@ -17634,7 +17634,7 @@
       </c>
       <c r="H340" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I340" s="12" t="inlineStr">
@@ -17682,7 +17682,7 @@
       <c r="G341" s="12" t="inlineStr"/>
       <c r="H341" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I341" s="12" t="inlineStr">
@@ -17730,7 +17730,7 @@
       <c r="G342" s="12" t="inlineStr"/>
       <c r="H342" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I342" s="12" t="inlineStr">
@@ -17782,7 +17782,7 @@
       </c>
       <c r="H343" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I343" s="12" t="inlineStr">
@@ -17834,7 +17834,7 @@
       </c>
       <c r="H344" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I344" s="12" t="inlineStr">
@@ -17882,7 +17882,7 @@
       <c r="G345" s="12" t="inlineStr"/>
       <c r="H345" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Conditional Continued Diafiltration</t>
+          <t>SMPL: Conditional Continued Diafiltration (block stack)</t>
         </is>
       </c>
       <c r="I345" s="12" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="H346" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Conditional Continued Diafiltration</t>
+          <t>SMPL: Conditional Continued Diafiltration (block stack)</t>
         </is>
       </c>
       <c r="I346" s="12" t="inlineStr">
@@ -17986,7 +17986,7 @@
       </c>
       <c r="H347" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Conditional Continued Diafiltration</t>
+          <t>SMPL: Conditional Continued Diafiltration (block stack)</t>
         </is>
       </c>
       <c r="I347" s="12" t="inlineStr">
@@ -18034,7 +18034,7 @@
       <c r="G348" s="12" t="inlineStr"/>
       <c r="H348" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Conditional Continued Diafiltration</t>
+          <t>SMPL: Conditional Continued Diafiltration (block stack)</t>
         </is>
       </c>
       <c r="I348" s="12" t="inlineStr">
@@ -18082,7 +18082,7 @@
       <c r="G349" s="12" t="inlineStr"/>
       <c r="H349" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Conditional Continued Diafiltration</t>
+          <t>SMPL: Conditional Continued Diafiltration (block stack)</t>
         </is>
       </c>
       <c r="I349" s="12" t="inlineStr">
@@ -18134,7 +18134,7 @@
       </c>
       <c r="H350" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Conditional Continued Diafiltration</t>
+          <t>SMPL: Conditional Continued Diafiltration (block stack)</t>
         </is>
       </c>
       <c r="I350" s="12" t="inlineStr">
@@ -18182,7 +18182,7 @@
       <c r="G351" s="12" t="inlineStr"/>
       <c r="H351" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Conditional Continued Diafiltration</t>
+          <t>SMPL: Conditional Continued Diafiltration (block stack)</t>
         </is>
       </c>
       <c r="I351" s="12" t="inlineStr">
@@ -18234,7 +18234,7 @@
       </c>
       <c r="H352" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Conditional Continued Diafiltration</t>
+          <t>SMPL: Conditional Continued Diafiltration (block stack)</t>
         </is>
       </c>
       <c r="I352" s="12" t="inlineStr">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="H353" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Conditional Continued Diafiltration</t>
+          <t>SMPL: Conditional Continued Diafiltration (block stack)</t>
         </is>
       </c>
       <c r="I353" s="12" t="inlineStr">
@@ -18338,7 +18338,7 @@
       </c>
       <c r="H354" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Conditional Continued Diafiltration</t>
+          <t>SMPL: Conditional Continued Diafiltration (block stack)</t>
         </is>
       </c>
       <c r="I354" s="12" t="inlineStr">
@@ -18390,7 +18390,7 @@
       </c>
       <c r="H355" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Conditional Continued Diafiltration</t>
+          <t>SMPL: Conditional Continued Diafiltration (block stack)</t>
         </is>
       </c>
       <c r="I355" s="12" t="inlineStr">
@@ -18442,7 +18442,7 @@
       </c>
       <c r="H356" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Conditional Continued Diafiltration</t>
+          <t>SMPL: Conditional Continued Diafiltration (block stack)</t>
         </is>
       </c>
       <c r="I356" s="12" t="inlineStr">
@@ -18494,7 +18494,7 @@
       </c>
       <c r="H357" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Conditional Continued Diafiltration</t>
+          <t>SMPL: Conditional Continued Diafiltration (block stack)</t>
         </is>
       </c>
       <c r="I357" s="12" t="inlineStr">
@@ -18542,7 +18542,7 @@
       <c r="G358" s="12" t="inlineStr"/>
       <c r="H358" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Conditional Continued Diafiltration</t>
+          <t>SMPL: Conditional Continued Diafiltration (block stack)</t>
         </is>
       </c>
       <c r="I358" s="12" t="inlineStr">
@@ -18594,7 +18594,7 @@
       </c>
       <c r="H359" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Conditional Continued Diafiltration</t>
+          <t>SMPL: Conditional Continued Diafiltration (block stack)</t>
         </is>
       </c>
       <c r="I359" s="12" t="inlineStr">
@@ -18646,7 +18646,7 @@
       </c>
       <c r="H360" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Conditional Continued Diafiltration</t>
+          <t>SMPL: Conditional Continued Diafiltration (block stack)</t>
         </is>
       </c>
       <c r="I360" s="12" t="inlineStr">
@@ -18698,7 +18698,7 @@
       </c>
       <c r="H361" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Conditional Continued Diafiltration</t>
+          <t>SMPL: Conditional Continued Diafiltration (block stack)</t>
         </is>
       </c>
       <c r="I361" s="12" t="inlineStr">
@@ -18746,7 +18746,7 @@
       <c r="G362" s="12" t="inlineStr"/>
       <c r="H362" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Conditional Continued Diafiltration</t>
+          <t>SMPL: Conditional Continued Diafiltration (block stack)</t>
         </is>
       </c>
       <c r="I362" s="12" t="inlineStr">
@@ -18798,7 +18798,7 @@
       </c>
       <c r="H363" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Conditional Continued Diafiltration</t>
+          <t>SMPL: Conditional Continued Diafiltration (block stack)</t>
         </is>
       </c>
       <c r="I363" s="12" t="inlineStr">
@@ -18846,7 +18846,7 @@
       <c r="G364" s="12" t="inlineStr"/>
       <c r="H364" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Conditional Continued Diafiltration</t>
+          <t>SMPL: Conditional Continued Diafiltration (block stack)</t>
         </is>
       </c>
       <c r="I364" s="12" t="inlineStr">
@@ -18898,7 +18898,7 @@
       </c>
       <c r="H365" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Conditional Continued Diafiltration</t>
+          <t>SMPL: Conditional Continued Diafiltration (block stack)</t>
         </is>
       </c>
       <c r="I365" s="12" t="inlineStr">
@@ -18950,7 +18950,7 @@
       </c>
       <c r="H366" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Conditional Continued Diafiltration</t>
+          <t>SMPL: Conditional Continued Diafiltration (block stack)</t>
         </is>
       </c>
       <c r="I366" s="12" t="inlineStr">
@@ -19002,7 +19002,7 @@
       </c>
       <c r="H367" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Conditional Continued Diafiltration</t>
+          <t>SMPL: Conditional Continued Diafiltration (block stack)</t>
         </is>
       </c>
       <c r="I367" s="12" t="inlineStr">
@@ -19054,7 +19054,7 @@
       </c>
       <c r="H368" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Conditional Continued Diafiltration</t>
+          <t>SMPL: Conditional Continued Diafiltration (block stack)</t>
         </is>
       </c>
       <c r="I368" s="12" t="inlineStr">
@@ -19106,7 +19106,7 @@
       </c>
       <c r="H369" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Conditional Continued Diafiltration</t>
+          <t>SMPL: Conditional Continued Diafiltration (block stack)</t>
         </is>
       </c>
       <c r="I369" s="12" t="inlineStr">
@@ -19158,7 +19158,7 @@
       </c>
       <c r="H370" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Conditional Continued Diafiltration</t>
+          <t>SMPL: Conditional Continued Diafiltration (block stack)</t>
         </is>
       </c>
       <c r="I370" s="12" t="inlineStr">
@@ -19210,7 +19210,7 @@
       </c>
       <c r="H371" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Conditional Continued Diafiltration</t>
+          <t>SMPL: Conditional Continued Diafiltration (block stack)</t>
         </is>
       </c>
       <c r="I371" s="12" t="inlineStr">
@@ -19262,7 +19262,7 @@
       </c>
       <c r="H372" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I372" s="12" t="inlineStr">
@@ -19310,7 +19310,7 @@
       <c r="G373" s="12" t="inlineStr"/>
       <c r="H373" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I373" s="12" t="inlineStr">
@@ -19362,7 +19362,7 @@
       </c>
       <c r="H374" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I374" s="12" t="inlineStr">
@@ -19414,7 +19414,7 @@
       </c>
       <c r="H375" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I375" s="12" t="inlineStr">
@@ -19466,7 +19466,7 @@
       </c>
       <c r="H376" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I376" s="12" t="inlineStr">
@@ -19518,7 +19518,7 @@
       </c>
       <c r="H377" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I377" s="12" t="inlineStr">
@@ -19566,7 +19566,7 @@
       <c r="G378" s="12" t="inlineStr"/>
       <c r="H378" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I378" s="12" t="inlineStr">
@@ -19618,7 +19618,7 @@
       </c>
       <c r="H379" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I379" s="12" t="inlineStr">
@@ -19666,7 +19666,7 @@
       <c r="G380" s="12" t="inlineStr"/>
       <c r="H380" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I380" s="12" t="inlineStr">
@@ -19718,7 +19718,7 @@
       </c>
       <c r="H381" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="I381" s="12" t="inlineStr">
@@ -19770,7 +19770,7 @@
       </c>
       <c r="H382" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Recovery Calculations &amp; Execution</t>
+          <t>SMPL: Recovery Calculations &amp; Execution (block stack)</t>
         </is>
       </c>
       <c r="I382" s="12" t="inlineStr">
@@ -19822,7 +19822,7 @@
       </c>
       <c r="H383" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Recovery Calculations &amp; Execution</t>
+          <t>SMPL: Recovery Calculations &amp; Execution (block stack)</t>
         </is>
       </c>
       <c r="I383" s="12" t="inlineStr">
@@ -19874,7 +19874,7 @@
       </c>
       <c r="H384" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Recovery Calculations &amp; Execution</t>
+          <t>SMPL: Recovery Calculations &amp; Execution (block stack)</t>
         </is>
       </c>
       <c r="I384" s="12" t="inlineStr">
@@ -19926,7 +19926,7 @@
       </c>
       <c r="H385" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Recovery Calculations &amp; Execution</t>
+          <t>SMPL: Recovery Calculations &amp; Execution (block stack)</t>
         </is>
       </c>
       <c r="I385" s="12" t="inlineStr">
@@ -19978,7 +19978,7 @@
       </c>
       <c r="H386" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Recovery Calculations &amp; Execution</t>
+          <t>SMPL: Recovery Calculations &amp; Execution (block stack)</t>
         </is>
       </c>
       <c r="I386" s="12" t="inlineStr">
@@ -20030,7 +20030,7 @@
       </c>
       <c r="H387" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Recovery Calculations &amp; Execution</t>
+          <t>SMPL: Recovery Calculations &amp; Execution (block stack)</t>
         </is>
       </c>
       <c r="I387" s="12" t="inlineStr">
@@ -20082,7 +20082,7 @@
       </c>
       <c r="H388" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Recovery Calculations &amp; Execution</t>
+          <t>SMPL: Recovery Calculations &amp; Execution (block stack)</t>
         </is>
       </c>
       <c r="I388" s="12" t="inlineStr">
@@ -20134,7 +20134,7 @@
       </c>
       <c r="H389" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Recovery Calculations &amp; Execution</t>
+          <t>SMPL: Recovery Calculations &amp; Execution (block stack)</t>
         </is>
       </c>
       <c r="I389" s="12" t="inlineStr">
@@ -20186,7 +20186,7 @@
       </c>
       <c r="H390" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Recovery Calculations &amp; Execution</t>
+          <t>SMPL: Recovery Calculations &amp; Execution (block stack)</t>
         </is>
       </c>
       <c r="I390" s="12" t="inlineStr">
@@ -20238,7 +20238,7 @@
       </c>
       <c r="H391" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Recovery Calculations &amp; Execution</t>
+          <t>SMPL: Recovery Calculations &amp; Execution (block stack)</t>
         </is>
       </c>
       <c r="I391" s="12" t="inlineStr">
@@ -20290,7 +20290,7 @@
       </c>
       <c r="H392" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Recovery Calculations &amp; Execution</t>
+          <t>SMPL: Recovery Calculations &amp; Execution (block stack)</t>
         </is>
       </c>
       <c r="I392" s="12" t="inlineStr">
@@ -20342,7 +20342,7 @@
       </c>
       <c r="H393" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Recovery Calculations &amp; Execution</t>
+          <t>SMPL: Recovery Calculations &amp; Execution (block stack)</t>
         </is>
       </c>
       <c r="I393" s="12" t="inlineStr">
@@ -20390,7 +20390,7 @@
       <c r="G394" s="12" t="inlineStr"/>
       <c r="H394" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Recovery Calculations &amp; Execution</t>
+          <t>SMPL: Recovery Calculations &amp; Execution (block stack)</t>
         </is>
       </c>
       <c r="I394" s="12" t="inlineStr">
@@ -20438,7 +20438,7 @@
       <c r="G395" s="12" t="inlineStr"/>
       <c r="H395" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Recovery Calculations &amp; Execution</t>
+          <t>SMPL: Recovery Calculations &amp; Execution (block stack)</t>
         </is>
       </c>
       <c r="I395" s="12" t="inlineStr">
@@ -20490,7 +20490,7 @@
       </c>
       <c r="H396" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Recovery Calculations &amp; Execution</t>
+          <t>SMPL: Recovery Calculations &amp; Execution (block stack)</t>
         </is>
       </c>
       <c r="I396" s="12" t="inlineStr">
@@ -20542,7 +20542,7 @@
       </c>
       <c r="H397" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Recovery Calculations &amp; Execution</t>
+          <t>SMPL: Recovery Calculations &amp; Execution (block stack)</t>
         </is>
       </c>
       <c r="I397" s="12" t="inlineStr">
@@ -20594,7 +20594,7 @@
       </c>
       <c r="H398" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Recovery Calculations &amp; Execution</t>
+          <t>SMPL: Recovery Calculations &amp; Execution (block stack)</t>
         </is>
       </c>
       <c r="I398" s="12" t="inlineStr">
@@ -20646,7 +20646,7 @@
       </c>
       <c r="H399" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Recovery Calculations &amp; Execution</t>
+          <t>SMPL: Recovery Calculations &amp; Execution (block stack)</t>
         </is>
       </c>
       <c r="I399" s="12" t="inlineStr">
@@ -20698,7 +20698,7 @@
       </c>
       <c r="H400" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Recovery Calculations &amp; Execution</t>
+          <t>SMPL: Recovery Calculations &amp; Execution (block stack)</t>
         </is>
       </c>
       <c r="I400" s="12" t="inlineStr">
@@ -20746,7 +20746,7 @@
       <c r="G401" s="12" t="inlineStr"/>
       <c r="H401" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Recovery Calculations &amp; Execution</t>
+          <t>SMPL: Recovery Calculations &amp; Execution (block stack)</t>
         </is>
       </c>
       <c r="I401" s="12" t="inlineStr">
@@ -20794,7 +20794,7 @@
       <c r="G402" s="12" t="inlineStr"/>
       <c r="H402" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Recovery Calculations &amp; Execution</t>
+          <t>SMPL: Recovery Calculations &amp; Execution (block stack)</t>
         </is>
       </c>
       <c r="I402" s="12" t="inlineStr">
@@ -20842,7 +20842,7 @@
       <c r="G403" s="12" t="inlineStr"/>
       <c r="H403" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Recovery Calculations &amp; Execution</t>
+          <t>SMPL: Recovery Calculations &amp; Execution (block stack)</t>
         </is>
       </c>
       <c r="I403" s="12" t="inlineStr">
@@ -20894,7 +20894,7 @@
       </c>
       <c r="H404" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Recovery Calculations &amp; Execution</t>
+          <t>SMPL: Recovery Calculations &amp; Execution (block stack)</t>
         </is>
       </c>
       <c r="I404" s="12" t="inlineStr">
@@ -20946,7 +20946,7 @@
       </c>
       <c r="H405" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Recovery Calculations &amp; Execution</t>
+          <t>SMPL: Recovery Calculations &amp; Execution (block stack)</t>
         </is>
       </c>
       <c r="I405" s="12" t="inlineStr">
@@ -20994,7 +20994,7 @@
       <c r="G406" s="12" t="inlineStr"/>
       <c r="H406" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Recovery Calculations &amp; Execution</t>
+          <t>SMPL: Recovery Calculations &amp; Execution (block stack)</t>
         </is>
       </c>
       <c r="I406" s="12" t="inlineStr">
@@ -21042,7 +21042,7 @@
       <c r="G407" s="12" t="inlineStr"/>
       <c r="H407" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Recovery Calculations &amp; Execution</t>
+          <t>SMPL: Recovery Calculations &amp; Execution (block stack)</t>
         </is>
       </c>
       <c r="I407" s="12" t="inlineStr">
@@ -21090,7 +21090,7 @@
       <c r="G408" s="12" t="inlineStr"/>
       <c r="H408" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Recovery Calculations &amp; Execution</t>
+          <t>SMPL: Recovery Calculations &amp; Execution (block stack)</t>
         </is>
       </c>
       <c r="I408" s="12" t="inlineStr">
@@ -21142,7 +21142,7 @@
       </c>
       <c r="H409" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Recovery Calculations &amp; Execution</t>
+          <t>SMPL: Recovery Calculations &amp; Execution (block stack)</t>
         </is>
       </c>
       <c r="I409" s="12" t="inlineStr">
@@ -21194,7 +21194,7 @@
       </c>
       <c r="H410" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Recovery Calculations &amp; Execution</t>
+          <t>SMPL: Recovery Calculations &amp; Execution (block stack)</t>
         </is>
       </c>
       <c r="I410" s="12" t="inlineStr">
@@ -21246,7 +21246,7 @@
       </c>
       <c r="H411" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Recovery Calculations &amp; Execution</t>
+          <t>SMPL: Recovery Calculations &amp; Execution (block stack)</t>
         </is>
       </c>
       <c r="I411" s="12" t="inlineStr">
@@ -21298,7 +21298,7 @@
       </c>
       <c r="H412" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Recovery Calculations &amp; Execution</t>
+          <t>SMPL: Recovery Calculations &amp; Execution (block stack)</t>
         </is>
       </c>
       <c r="I412" s="12" t="inlineStr">
@@ -21350,7 +21350,7 @@
       </c>
       <c r="H413" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Recovery Calculations &amp; Execution</t>
+          <t>SMPL: Recovery Calculations &amp; Execution (block stack)</t>
         </is>
       </c>
       <c r="I413" s="12" t="inlineStr">
@@ -21402,7 +21402,7 @@
       </c>
       <c r="H414" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Recovery Calculations &amp; Execution</t>
+          <t>SMPL: Recovery Calculations &amp; Execution (block stack)</t>
         </is>
       </c>
       <c r="I414" s="12" t="inlineStr">
@@ -21454,7 +21454,7 @@
       </c>
       <c r="H415" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Dilution Decision &amp; Calculations</t>
+          <t>SMPL: Dilution Decision &amp; Calculations (block stack)</t>
         </is>
       </c>
       <c r="I415" s="12" t="inlineStr">
@@ -21506,7 +21506,7 @@
       </c>
       <c r="H416" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Dilution Decision &amp; Calculations</t>
+          <t>SMPL: Dilution Decision &amp; Calculations (block stack)</t>
         </is>
       </c>
       <c r="I416" s="12" t="inlineStr">
@@ -21558,7 +21558,7 @@
       </c>
       <c r="H417" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Dilution Decision &amp; Calculations</t>
+          <t>SMPL: Dilution Decision &amp; Calculations (block stack)</t>
         </is>
       </c>
       <c r="I417" s="12" t="inlineStr">
@@ -21610,7 +21610,7 @@
       </c>
       <c r="H418" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Dilution Decision &amp; Calculations</t>
+          <t>SMPL: Dilution Decision &amp; Calculations (block stack)</t>
         </is>
       </c>
       <c r="I418" s="12" t="inlineStr">
@@ -21662,7 +21662,7 @@
       </c>
       <c r="H419" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Dilution Decision &amp; Calculations</t>
+          <t>SMPL: Dilution Decision &amp; Calculations (block stack)</t>
         </is>
       </c>
       <c r="I419" s="12" t="inlineStr">
@@ -21710,7 +21710,7 @@
       <c r="G420" s="12" t="inlineStr"/>
       <c r="H420" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Dilution Decision &amp; Calculations</t>
+          <t>SMPL: Dilution Decision &amp; Calculations (block stack)</t>
         </is>
       </c>
       <c r="I420" s="12" t="inlineStr">
@@ -21758,7 +21758,7 @@
       <c r="G421" s="12" t="inlineStr"/>
       <c r="H421" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Dilution Decision &amp; Calculations</t>
+          <t>SMPL: Dilution Decision &amp; Calculations (block stack)</t>
         </is>
       </c>
       <c r="I421" s="12" t="inlineStr">
@@ -21810,7 +21810,7 @@
       </c>
       <c r="H422" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Dilution Decision &amp; Calculations</t>
+          <t>SMPL: Dilution Decision &amp; Calculations (block stack)</t>
         </is>
       </c>
       <c r="I422" s="12" t="inlineStr">
@@ -21862,7 +21862,7 @@
       </c>
       <c r="H423" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Dilution Decision &amp; Calculations</t>
+          <t>SMPL: Dilution Decision &amp; Calculations (block stack)</t>
         </is>
       </c>
       <c r="I423" s="12" t="inlineStr">
@@ -21914,7 +21914,7 @@
       </c>
       <c r="H424" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Dilution Decision &amp; Calculations</t>
+          <t>SMPL: Dilution Decision &amp; Calculations (block stack)</t>
         </is>
       </c>
       <c r="I424" s="12" t="inlineStr">
@@ -21962,7 +21962,7 @@
       <c r="G425" s="12" t="inlineStr"/>
       <c r="H425" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Dilution Decision &amp; Calculations</t>
+          <t>SMPL: Dilution Decision &amp; Calculations (block stack)</t>
         </is>
       </c>
       <c r="I425" s="12" t="inlineStr">
@@ -22014,7 +22014,7 @@
       </c>
       <c r="H426" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Dilution Decision &amp; Calculations</t>
+          <t>SMPL: Dilution Decision &amp; Calculations (block stack)</t>
         </is>
       </c>
       <c r="I426" s="12" t="inlineStr">
@@ -22066,7 +22066,7 @@
       </c>
       <c r="H427" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Dilution Decision &amp; Calculations</t>
+          <t>SMPL: Dilution Decision &amp; Calculations (block stack)</t>
         </is>
       </c>
       <c r="I427" s="12" t="inlineStr">
@@ -22118,7 +22118,7 @@
       </c>
       <c r="H428" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Dilution Decision &amp; Calculations</t>
+          <t>SMPL: Dilution Decision &amp; Calculations (block stack)</t>
         </is>
       </c>
       <c r="I428" s="12" t="inlineStr">
@@ -22170,7 +22170,7 @@
       </c>
       <c r="H429" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Dilution Decision &amp; Calculations</t>
+          <t>SMPL: Dilution Decision &amp; Calculations (block stack)</t>
         </is>
       </c>
       <c r="I429" s="12" t="inlineStr">
@@ -22222,7 +22222,7 @@
       </c>
       <c r="H430" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Dilution Decision &amp; Calculations</t>
+          <t>SMPL: Dilution Decision &amp; Calculations (block stack)</t>
         </is>
       </c>
       <c r="I430" s="12" t="inlineStr">
@@ -22274,7 +22274,7 @@
       </c>
       <c r="H431" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Dilution Decision &amp; Calculations</t>
+          <t>SMPL: Dilution Decision &amp; Calculations (block stack)</t>
         </is>
       </c>
       <c r="I431" s="12" t="inlineStr">
@@ -22326,7 +22326,7 @@
       </c>
       <c r="H432" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Dilution Decision &amp; Calculations</t>
+          <t>SMPL: Dilution Decision &amp; Calculations (block stack)</t>
         </is>
       </c>
       <c r="I432" s="12" t="inlineStr">
@@ -22378,7 +22378,7 @@
       </c>
       <c r="H433" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Dilution Decision &amp; Calculations</t>
+          <t>SMPL: Dilution Decision &amp; Calculations (block stack)</t>
         </is>
       </c>
       <c r="I433" s="12" t="inlineStr">
@@ -22426,7 +22426,7 @@
       <c r="G434" s="12" t="inlineStr"/>
       <c r="H434" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Dilution Decision &amp; Calculations</t>
+          <t>SMPL: Dilution Decision &amp; Calculations (block stack)</t>
         </is>
       </c>
       <c r="I434" s="12" t="inlineStr">
@@ -22474,7 +22474,7 @@
       <c r="G435" s="12" t="inlineStr"/>
       <c r="H435" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Dilution Decision &amp; Calculations</t>
+          <t>SMPL: Dilution Decision &amp; Calculations (block stack)</t>
         </is>
       </c>
       <c r="I435" s="12" t="inlineStr">
@@ -22522,7 +22522,7 @@
       <c r="G436" s="12" t="inlineStr"/>
       <c r="H436" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Dilution Decision &amp; Calculations</t>
+          <t>SMPL: Dilution Decision &amp; Calculations (block stack)</t>
         </is>
       </c>
       <c r="I436" s="12" t="inlineStr">
@@ -22570,7 +22570,7 @@
       <c r="G437" s="12" t="inlineStr"/>
       <c r="H437" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Dilution Decision &amp; Calculations</t>
+          <t>SMPL: Dilution Decision &amp; Calculations (block stack)</t>
         </is>
       </c>
       <c r="I437" s="12" t="inlineStr">
@@ -22622,7 +22622,7 @@
       </c>
       <c r="H438" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Dilution Decision &amp; Calculations</t>
+          <t>SMPL: Dilution Decision &amp; Calculations (block stack)</t>
         </is>
       </c>
       <c r="I438" s="12" t="inlineStr">
@@ -22670,7 +22670,7 @@
       <c r="G439" s="12" t="inlineStr"/>
       <c r="H439" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Dilution Decision &amp; Calculations</t>
+          <t>SMPL: Dilution Decision &amp; Calculations (block stack)</t>
         </is>
       </c>
       <c r="I439" s="12" t="inlineStr">
@@ -22718,7 +22718,7 @@
       <c r="G440" s="12" t="inlineStr"/>
       <c r="H440" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Dilution Decision &amp; Calculations</t>
+          <t>SMPL: Dilution Decision &amp; Calculations (block stack)</t>
         </is>
       </c>
       <c r="I440" s="12" t="inlineStr">
@@ -22770,7 +22770,7 @@
       </c>
       <c r="H441" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Dilution Decision &amp; Calculations</t>
+          <t>SMPL: Dilution Decision &amp; Calculations (block stack)</t>
         </is>
       </c>
       <c r="I441" s="12" t="inlineStr">
@@ -22822,7 +22822,7 @@
       </c>
       <c r="H442" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Dilution Decision &amp; Calculations</t>
+          <t>SMPL: Dilution Decision &amp; Calculations (block stack)</t>
         </is>
       </c>
       <c r="I442" s="12" t="inlineStr">
@@ -22874,7 +22874,7 @@
       </c>
       <c r="H443" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Dilution Decision &amp; Calculations</t>
+          <t>SMPL: Dilution Decision &amp; Calculations (block stack)</t>
         </is>
       </c>
       <c r="I443" s="12" t="inlineStr">
@@ -22922,7 +22922,7 @@
       <c r="G444" s="12" t="inlineStr"/>
       <c r="H444" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Dilution Decision &amp; Calculations</t>
+          <t>SMPL: Dilution Decision &amp; Calculations (block stack)</t>
         </is>
       </c>
       <c r="I444" s="12" t="inlineStr">
@@ -22970,7 +22970,7 @@
       <c r="G445" s="12" t="inlineStr"/>
       <c r="H445" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Dilution Decision &amp; Calculations</t>
+          <t>SMPL: Dilution Decision &amp; Calculations (block stack)</t>
         </is>
       </c>
       <c r="I445" s="12" t="inlineStr">
@@ -23022,7 +23022,7 @@
       </c>
       <c r="H446" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Dilution Decision &amp; Calculations</t>
+          <t>SMPL: Dilution Decision &amp; Calculations (block stack)</t>
         </is>
       </c>
       <c r="I446" s="12" t="inlineStr">
@@ -23074,7 +23074,7 @@
       </c>
       <c r="H447" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Dilution Decision &amp; Calculations</t>
+          <t>SMPL: Dilution Decision &amp; Calculations (block stack)</t>
         </is>
       </c>
       <c r="I447" s="12" t="inlineStr">
@@ -23126,7 +23126,7 @@
       </c>
       <c r="H448" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Dilution Decision &amp; Calculations</t>
+          <t>SMPL: Dilution Decision &amp; Calculations (block stack)</t>
         </is>
       </c>
       <c r="I448" s="12" t="inlineStr">
@@ -23178,7 +23178,7 @@
       </c>
       <c r="H449" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Dilution Decision &amp; Calculations</t>
+          <t>SMPL: Dilution Decision &amp; Calculations (block stack)</t>
         </is>
       </c>
       <c r="I449" s="12" t="inlineStr">
@@ -23230,7 +23230,7 @@
       </c>
       <c r="H450" s="12" t="inlineStr">
         <is>
-          <t>SMPL: PFI Storage Vessel, SHC Filter &amp; Store</t>
+          <t>SMPL: PFI Storage Vessel, SHC Filter &amp; Store (block stack)</t>
         </is>
       </c>
       <c r="I450" s="12" t="inlineStr">
@@ -23282,7 +23282,7 @@
       </c>
       <c r="H451" s="12" t="inlineStr">
         <is>
-          <t>SMPL: PFI Storage Vessel, SHC Filter &amp; Store</t>
+          <t>SMPL: PFI Storage Vessel, SHC Filter &amp; Store (block stack)</t>
         </is>
       </c>
       <c r="I451" s="12" t="inlineStr">
@@ -23334,7 +23334,7 @@
       </c>
       <c r="H452" s="12" t="inlineStr">
         <is>
-          <t>SMPL: PFI Storage Vessel, SHC Filter &amp; Store</t>
+          <t>SMPL: PFI Storage Vessel, SHC Filter &amp; Store (block stack)</t>
         </is>
       </c>
       <c r="I452" s="12" t="inlineStr">
@@ -23386,7 +23386,7 @@
       </c>
       <c r="H453" s="12" t="inlineStr">
         <is>
-          <t>SMPL: PFI Storage Vessel, SHC Filter &amp; Store</t>
+          <t>SMPL: PFI Storage Vessel, SHC Filter &amp; Store (block stack)</t>
         </is>
       </c>
       <c r="I453" s="12" t="inlineStr">
@@ -23434,7 +23434,7 @@
       <c r="G454" s="12" t="inlineStr"/>
       <c r="H454" s="12" t="inlineStr">
         <is>
-          <t>SMPL: PFI Storage Vessel, SHC Filter &amp; Store</t>
+          <t>SMPL: PFI Storage Vessel, SHC Filter &amp; Store (block stack)</t>
         </is>
       </c>
       <c r="I454" s="12" t="inlineStr">
@@ -23482,7 +23482,7 @@
       <c r="G455" s="12" t="inlineStr"/>
       <c r="H455" s="12" t="inlineStr">
         <is>
-          <t>SMPL: PFI Storage Vessel, SHC Filter &amp; Store</t>
+          <t>SMPL: PFI Storage Vessel, SHC Filter &amp; Store (block stack)</t>
         </is>
       </c>
       <c r="I455" s="12" t="inlineStr">
@@ -23530,7 +23530,7 @@
       <c r="G456" s="12" t="inlineStr"/>
       <c r="H456" s="12" t="inlineStr">
         <is>
-          <t>SMPL: PFI Storage Vessel, SHC Filter &amp; Store</t>
+          <t>SMPL: PFI Storage Vessel, SHC Filter &amp; Store (block stack)</t>
         </is>
       </c>
       <c r="I456" s="12" t="inlineStr">
@@ -23582,7 +23582,7 @@
       </c>
       <c r="H457" s="12" t="inlineStr">
         <is>
-          <t>SMPL: PFI Storage Vessel, SHC Filter &amp; Store</t>
+          <t>SMPL: PFI Storage Vessel, SHC Filter &amp; Store (block stack)</t>
         </is>
       </c>
       <c r="I457" s="12" t="inlineStr">
@@ -23634,7 +23634,7 @@
       </c>
       <c r="H458" s="12" t="inlineStr">
         <is>
-          <t>SMPL: PFI Storage Vessel, SHC Filter &amp; Store</t>
+          <t>SMPL: PFI Storage Vessel, SHC Filter &amp; Store (block stack)</t>
         </is>
       </c>
       <c r="I458" s="12" t="inlineStr">
@@ -23686,7 +23686,7 @@
       </c>
       <c r="H459" s="12" t="inlineStr">
         <is>
-          <t>SMPL: PFI Storage Vessel, SHC Filter &amp; Store</t>
+          <t>SMPL: PFI Storage Vessel, SHC Filter &amp; Store (block stack)</t>
         </is>
       </c>
       <c r="I459" s="12" t="inlineStr">
@@ -23734,7 +23734,7 @@
       <c r="G460" s="12" t="inlineStr"/>
       <c r="H460" s="12" t="inlineStr">
         <is>
-          <t>SMPL: PFI Storage Vessel, SHC Filter &amp; Store</t>
+          <t>SMPL: PFI Storage Vessel, SHC Filter &amp; Store (block stack)</t>
         </is>
       </c>
       <c r="I460" s="12" t="inlineStr">
@@ -23782,7 +23782,7 @@
       <c r="G461" s="12" t="inlineStr"/>
       <c r="H461" s="12" t="inlineStr">
         <is>
-          <t>SMPL: PFI Storage Vessel, SHC Filter &amp; Store</t>
+          <t>SMPL: PFI Storage Vessel, SHC Filter &amp; Store (block stack)</t>
         </is>
       </c>
       <c r="I461" s="12" t="inlineStr">
@@ -23834,7 +23834,7 @@
       </c>
       <c r="H462" s="12" t="inlineStr">
         <is>
-          <t>SMPL: PFI Storage Vessel, SHC Filter &amp; Store</t>
+          <t>SMPL: PFI Storage Vessel, SHC Filter &amp; Store (block stack)</t>
         </is>
       </c>
       <c r="I462" s="12" t="inlineStr">
@@ -23886,7 +23886,7 @@
       </c>
       <c r="H463" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Post-Processing: Cassette Re-use &amp; Sanitization</t>
+          <t>SMPL: Post-Processing: Cassette Re-use &amp; Sanitization (block stack)</t>
         </is>
       </c>
       <c r="I463" s="12" t="inlineStr">
@@ -23934,7 +23934,7 @@
       <c r="G464" s="12" t="inlineStr"/>
       <c r="H464" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Post-Processing: Cassette Re-use &amp; Sanitization</t>
+          <t>SMPL: Post-Processing: Cassette Re-use &amp; Sanitization (block stack)</t>
         </is>
       </c>
       <c r="I464" s="12" t="inlineStr">
@@ -23986,7 +23986,7 @@
       </c>
       <c r="H465" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Post-Processing: Cassette Re-use &amp; Sanitization</t>
+          <t>SMPL: Post-Processing: Cassette Re-use &amp; Sanitization (block stack)</t>
         </is>
       </c>
       <c r="I465" s="12" t="inlineStr">
@@ -24034,7 +24034,7 @@
       <c r="G466" s="12" t="inlineStr"/>
       <c r="H466" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Post-Processing: Cassette Re-use &amp; Sanitization</t>
+          <t>SMPL: Post-Processing: Cassette Re-use &amp; Sanitization (block stack)</t>
         </is>
       </c>
       <c r="I466" s="12" t="inlineStr">
@@ -24082,7 +24082,7 @@
       <c r="G467" s="12" t="inlineStr"/>
       <c r="H467" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Post-Processing: Cassette Re-use &amp; Sanitization</t>
+          <t>SMPL: Post-Processing: Cassette Re-use &amp; Sanitization (block stack)</t>
         </is>
       </c>
       <c r="I467" s="12" t="inlineStr">
@@ -24130,7 +24130,7 @@
       <c r="G468" s="12" t="inlineStr"/>
       <c r="H468" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Post-Processing: Cassette Re-use &amp; Sanitization</t>
+          <t>SMPL: Post-Processing: Cassette Re-use &amp; Sanitization (block stack)</t>
         </is>
       </c>
       <c r="I468" s="12" t="inlineStr">
@@ -24182,7 +24182,7 @@
       </c>
       <c r="H469" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Post-Processing: Cassette Re-use &amp; Sanitization</t>
+          <t>SMPL: Post-Processing: Cassette Re-use &amp; Sanitization (block stack)</t>
         </is>
       </c>
       <c r="I469" s="12" t="inlineStr">
@@ -24234,7 +24234,7 @@
       </c>
       <c r="H470" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Post-Processing: Cassette Re-use &amp; Sanitization</t>
+          <t>SMPL: Post-Processing: Cassette Re-use &amp; Sanitization (block stack)</t>
         </is>
       </c>
       <c r="I470" s="12" t="inlineStr">
@@ -24282,7 +24282,7 @@
       <c r="G471" s="12" t="inlineStr"/>
       <c r="H471" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Post-Processing: Cassette Re-use &amp; Sanitization</t>
+          <t>SMPL: Post-Processing: Cassette Re-use &amp; Sanitization (block stack)</t>
         </is>
       </c>
       <c r="I471" s="12" t="inlineStr">
@@ -24330,7 +24330,7 @@
       <c r="G472" s="12" t="inlineStr"/>
       <c r="H472" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Post-Processing: Cassette Re-use &amp; Sanitization</t>
+          <t>SMPL: Post-Processing: Cassette Re-use &amp; Sanitization (block stack)</t>
         </is>
       </c>
       <c r="I472" s="12" t="inlineStr">
@@ -24378,7 +24378,7 @@
       <c r="G473" s="12" t="inlineStr"/>
       <c r="H473" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Post-Processing: Cassette Re-use &amp; Sanitization</t>
+          <t>SMPL: Post-Processing: Cassette Re-use &amp; Sanitization (block stack)</t>
         </is>
       </c>
       <c r="I473" s="12" t="inlineStr">
@@ -24430,7 +24430,7 @@
       </c>
       <c r="H474" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Post-Processing: Cassette Re-use &amp; Sanitization</t>
+          <t>SMPL: Post-Processing: Cassette Re-use &amp; Sanitization (block stack)</t>
         </is>
       </c>
       <c r="I474" s="12" t="inlineStr">
@@ -24482,7 +24482,7 @@
       </c>
       <c r="H475" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Post-Processing: Cassette Re-use &amp; Sanitization</t>
+          <t>SMPL: Post-Processing: Cassette Re-use &amp; Sanitization (block stack)</t>
         </is>
       </c>
       <c r="I475" s="12" t="inlineStr">
@@ -24534,7 +24534,7 @@
       </c>
       <c r="H476" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Post-Processing: Cassette Re-use &amp; Sanitization</t>
+          <t>SMPL: Post-Processing: Cassette Re-use &amp; Sanitization (block stack)</t>
         </is>
       </c>
       <c r="I476" s="12" t="inlineStr">
@@ -24586,7 +24586,7 @@
       </c>
       <c r="H477" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Post-Processing: Cassette Re-use &amp; Sanitization</t>
+          <t>SMPL: Post-Processing: Cassette Re-use &amp; Sanitization (block stack)</t>
         </is>
       </c>
       <c r="I477" s="12" t="inlineStr">
@@ -26314,7 +26314,7 @@
       <c r="G512" s="12" t="inlineStr"/>
       <c r="H512" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Record CIPDS / Skid / Cassette Information</t>
+          <t>SMPL: Record CIPDS / Skid / Cassette Information (block stack)</t>
         </is>
       </c>
       <c r="I512" s="12" t="inlineStr">
@@ -28971,16 +28971,16 @@
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Product Vessel Weigh</t>
+          <t>SMPL: Incoming Product Information (Weight / Concentration / DLIMS)</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>(reusable — instantiated in-line)</t>
+          <t>VI §7</t>
         </is>
       </c>
       <c r="E9" s="12" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
@@ -28994,16 +28994,16 @@
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Incoming Product Information (Weight / Concentration / DLIMS)</t>
+          <t>SMPL: Product Vessel Weigh</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>VI §7</t>
+          <t>(reusable — instantiated in-line)</t>
         </is>
       </c>
       <c r="E10" s="12" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -29040,7 +29040,7 @@
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Multi-Variable Calculation (3-4 operand)</t>
+          <t>SMPL: Multi-Variable Calculation (3-input / ranged)</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
@@ -29068,11 +29068,11 @@
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>(reusable — instantiated in-line)</t>
+          <t>CDF §9</t>
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
@@ -29137,11 +29137,11 @@
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>CDF §9, CDF §25, VI §19</t>
+          <t>CDF §25, VI §19</t>
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17">
@@ -29316,7 +29316,7 @@
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>SMPL: VI Treatment Vessel Setup (Comprehensive)</t>
+          <t>SMPL: VI Treatment Vessel Setup</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
@@ -29362,7 +29362,7 @@
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Incubation Timing &amp; Incubated Sample</t>
+          <t>SMPL: Incubation Timing &amp; Incubated Sample (block stack)</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
@@ -29385,7 +29385,7 @@
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Starting / Transfer Temperature Decision</t>
+          <t>SMPL: Starting / Transfer Temperature Decision (block stack)</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -29408,7 +29408,7 @@
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Store VI Product &amp; Hold-Time Link</t>
+          <t>SMPL: Store VI Product &amp; Hold-Time Link (block stack)</t>
         </is>
       </c>
       <c r="D28" s="12" t="inlineStr">
@@ -29431,7 +29431,7 @@
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Record CIPDS / Skid / Cassette Information</t>
+          <t>SMPL: Record CIPDS / Skid / Cassette Information (block stack)</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
@@ -29454,7 +29454,7 @@
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Run Skid Recipe (Batch ID, Start, Setpoints)</t>
+          <t>SMPL: Run Skid Recipe (block stack)</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
@@ -29477,7 +29477,7 @@
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Calculate Minimum Membrane Surface Area</t>
+          <t>SMPL: Minimum Membrane Surface Area (block stack)</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
@@ -29500,7 +29500,7 @@
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Process Input Calculations</t>
+          <t>SMPL: Process Input Calculations (calc-block stack)</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
@@ -29546,7 +29546,7 @@
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Conditional Continued Diafiltration</t>
+          <t>SMPL: Conditional Continued Diafiltration (block stack)</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr">
@@ -29569,7 +29569,7 @@
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Recovery Calculations &amp; Execution</t>
+          <t>SMPL: Recovery Calculations &amp; Execution (block stack)</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
@@ -29592,7 +29592,7 @@
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Dilution Decision &amp; Calculations</t>
+          <t>SMPL: Dilution Decision &amp; Calculations (block stack)</t>
         </is>
       </c>
       <c r="D36" s="12" t="inlineStr">
@@ -29615,7 +29615,7 @@
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>SMPL: PFI Storage Vessel, SHC Filter &amp; Store</t>
+          <t>SMPL: PFI Storage Vessel, SHC Filter &amp; Store (block stack)</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
@@ -29638,7 +29638,7 @@
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>SMPL: Post-Processing: Cassette Re-use &amp; Sanitization</t>
+          <t>SMPL: Post-Processing: Cassette Re-use &amp; Sanitization (block stack)</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
